--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ergebnis-ValueSet fuer die allgemeine und die spezifische Kultur: Wachstum oder kein Wachstum. Ein unbestimmbares Ergebnis wird nicht ueber value[x], sondern ueber Observation.dataAbsentReason abgebildet.</t>
+    <t>Ergebnis-ValueSet fuer die allgemeine und die spezifische Kultur: Wachstum, kein Wachstum oder ein nicht eindeutiges Ergebnis. Wie viel gewachsen ist, sagt nicht dieses ValueSet, sondern die Keimzahl. Ein unbestimmbares Ergebnis wird nicht ueber value[x], sondern ueber Observation.dataAbsentReason abgebildet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>No growth (qualifier value)</t>
+  </si>
+  <si>
+    <t>280414007</t>
+  </si>
+  <si>
+    <t>Equivocal result</t>
   </si>
   <si>
     <t/>
@@ -384,7 +390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -420,15 +426,23 @@
         <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-kultur-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
